--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3814097435289842</v>
+        <v>0.3814097435289841</v>
       </c>
       <c r="C2" t="n">
         <v>0.2161633346665067</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3814097435289842</v>
+        <v>0.3814097435289841</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,16 +474,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3433500649575789</v>
+        <v>0.343350064957579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1972059345704636</v>
+        <v>0.1972059345704637</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04317356680052986</v>
+        <v>-0.04317356680052992</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156876</v>
+        <v>0.7298736967156877</v>
       </c>
       <c r="F2" t="n">
         <v>0.1266840836012862</v>
@@ -746,11 +746,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3433500649575789</v>
+        <v>0.343350064957579</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04317356680052986, 0.7298736967156876)</t>
+          <t>(-0.04317356680052992, 0.7298736967156877)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.343350064957579</v>
+        <v>0.3433500649575789</v>
       </c>
       <c r="C2" t="n">
         <v>0.1972059345704637</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.343350064957579</v>
+        <v>0.3433500649575789</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,16 +474,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3433500649575789</v>
+        <v>0.343350064957579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1972059345704636</v>
+        <v>0.1972059345704637</v>
       </c>
       <c r="D2" t="n">
         <v>-0.04317356680052986</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156876</v>
+        <v>0.7298736967156878</v>
       </c>
       <c r="F2" t="n">
         <v>0.1266840836012862</v>
@@ -746,11 +746,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3433500649575789</v>
+        <v>0.343350064957579</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04317356680052986, 0.7298736967156876)</t>
+          <t>(-0.04317356680052986, 0.7298736967156878)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -477,13 +477,13 @@
         <v>0.3433500649575789</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1972059345704637</v>
+        <v>0.1972059345704636</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04317356680052981</v>
+        <v>-0.04317356680052986</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156877</v>
+        <v>0.7298736967156876</v>
       </c>
       <c r="F2" t="n">
         <v>0.1266840836012862</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.043173566800529806, 0.7298736967156877)</t>
+          <t>(-0.04317356680052986, 0.7298736967156876)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -477,13 +477,13 @@
         <v>0.343350064957579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1972059345704637</v>
+        <v>0.1972059345704636</v>
       </c>
       <c r="D2" t="n">
         <v>-0.04317356680052986</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156878</v>
+        <v>0.7298736967156876</v>
       </c>
       <c r="F2" t="n">
         <v>0.1266840836012862</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04317356680052986, 0.7298736967156878)</t>
+          <t>(-0.04317356680052986, 0.7298736967156876)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,19 +474,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.343350064957579</v>
+        <v>0.3807106881577678</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1972059345704636</v>
+        <v>0.1915944011631294</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04317356680052986</v>
+        <v>0.005185661878034098</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156876</v>
+        <v>0.7562357144375014</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1266840836012862</v>
+        <v>0.08881141439205954</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,91 +521,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2042069139579306</v>
+        <v>0.2155252995235383</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1397354834727927</v>
+        <v>0.2141460762471432</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1328235669188882</v>
+        <v>0.2083046752448036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1312995365562757</v>
+        <v>0.1296084629134711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09685384660951525</v>
+        <v>0.04095076006414229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03142669020726577</v>
+        <v>0.03850308374899781</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0237975154165268</v>
+        <v>0.03039970186039237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01895745575814135</v>
+        <v>0.02160723836517343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01664357494963683</v>
+        <v>0.01947320284268365</v>
       </c>
     </row>
     <row r="11">
@@ -615,107 +615,57 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01661438051166758</v>
+        <v>0.01913093213801348</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01434213577797507</v>
+        <v>0.01635509352901347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01412612661969504</v>
+        <v>0.01539871965809689</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01383197122165584</v>
+        <v>0.01381842401551001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01274533967146507</v>
+        <v>0.01224934641120925</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01182571997421722</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>organization_HR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.01083742936374872</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>job_family_Communications</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.01072640773453997</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>job_family_Marketing</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.009638154290173642</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>job_family_Supply_Chain</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.009459091934239276</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>job_family_IT_and_Digital</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.009367407417335353</v>
+        <v>0.004528983437811327</v>
       </c>
     </row>
   </sheetData>
@@ -746,11 +696,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.343350064957579</v>
+        <v>0.3807106881577678</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04317356680052986, 0.7298736967156876)</t>
+          <t>(0.005185661878034098, 0.7562357144375014)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -480,7 +480,7 @@
         <v>0.1915944011631294</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005185661878034098</v>
+        <v>0.005185661878034153</v>
       </c>
       <c r="E2" t="n">
         <v>0.7562357144375014</v>
@@ -700,7 +700,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(0.005185661878034098, 0.7562357144375014)</t>
+          <t>(0.0051856618780341535, 0.7562357144375014)</t>
         </is>
       </c>
     </row>
